--- a/Q4/表3_Q4-3.xlsx
+++ b/Q4/表3_Q4-3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="表3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -503,11 +503,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6:10-6:20</t>
+          <t>10:00-10:10</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2151</v>
+        <v>3.389</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -537,11 +537,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10:00-10:10</t>
+          <t>12:50-13:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.389</v>
+        <v>16.1045</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -571,11 +571,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12:50-13:00</t>
+          <t>13:10-13:40</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>16.1045</v>
+        <v>94.428</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -605,11 +605,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13:10-13:40</t>
+          <t>14:20-15:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>94.428</v>
+        <v>225.4734</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -639,11 +639,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14:20-15:00</t>
+          <t>15:50-16:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>225.4734</v>
+        <v>23.7215</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -673,11 +673,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15:50-16:00</t>
+          <t>17:00-18:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23.7215</v>
+        <v>108.3021</v>
       </c>
     </row>
     <row r="9">
@@ -688,14 +688,6 @@
       </c>
       <c r="D9" t="n">
         <v>151.807</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>17:00-18:00</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>108.3021</v>
       </c>
     </row>
   </sheetData>
